--- a/Mumbai-July-2025.xlsx
+++ b/Mumbai-July-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="146">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Mumbai</t>
   </si>
   <si>
@@ -319,28 +322,28 @@
     <t>MH02GH2432</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>ETIOS</t>
   </si>
   <si>
-    <t>HYRIDER</t>
-  </si>
-  <si>
-    <t>Fortuner</t>
-  </si>
-  <si>
-    <t>CITRON</t>
-  </si>
-  <si>
-    <t>TATA TIGORE</t>
+    <t>HYRYDER</t>
+  </si>
+  <si>
+    <t>FORTUNER</t>
+  </si>
+  <si>
+    <t>CITROEN</t>
+  </si>
+  <si>
+    <t>TATA TIGOR</t>
   </si>
   <si>
     <t>DZIRE</t>
   </si>
   <si>
-    <t>BYD</t>
+    <t>BYD E6</t>
   </si>
   <si>
     <t>CAMRY</t>
@@ -349,13 +352,13 @@
     <t>INVICTO</t>
   </si>
   <si>
-    <t>Hycross</t>
-  </si>
-  <si>
-    <t>Merc E</t>
-  </si>
-  <si>
-    <t>5 Series</t>
+    <t>HYCROSS</t>
+  </si>
+  <si>
+    <t>MERCEDES E</t>
+  </si>
+  <si>
+    <t>5 SERIES</t>
   </si>
   <si>
     <t>URBANIA</t>
@@ -364,9 +367,6 @@
     <t>XUV 400</t>
   </si>
   <si>
-    <t>XUV 401</t>
-  </si>
-  <si>
     <t>24/04/2019</t>
   </si>
   <si>
@@ -403,9 +403,6 @@
     <t>27/02/2025</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>21/09/2021</t>
   </si>
   <si>
@@ -415,7 +412,13 @@
     <t>27/04/2023</t>
   </si>
   <si>
+    <t>30/09/2021</t>
+  </si>
+  <si>
     <t>21/04/2025</t>
+  </si>
+  <si>
+    <t>14/04/2023</t>
   </si>
   <si>
     <t>27/05/2025</t>
@@ -810,10 +813,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z74"/>
+  <dimension ref="A1:AA74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -892,25 +895,28 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:26">
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>119</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G2" t="s">
         <v>117</v>
@@ -973,24 +979,24 @@
         <v>53.14</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>120</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G3" t="s">
         <v>117</v>
@@ -1053,24 +1059,24 @@
         <v>45.91</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>121</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G4" s="2">
         <v>44206</v>
@@ -1133,24 +1139,24 @@
         <v>55.58</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>122</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G5" t="s">
         <v>118</v>
@@ -1213,24 +1219,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>123</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G6" s="2">
         <v>43587</v>
@@ -1293,24 +1299,24 @@
         <v>63.7</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>124</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G7" t="s">
         <v>119</v>
@@ -1373,24 +1379,24 @@
         <v>64.47</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>125</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G8" s="2">
         <v>44899</v>
@@ -1453,24 +1459,24 @@
         <v>40.4</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>126</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G9" s="2">
         <v>44899</v>
@@ -1533,24 +1539,24 @@
         <v>36.78</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>127</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G10" s="2">
         <v>44899</v>
@@ -1613,24 +1619,24 @@
         <v>57.91</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>128</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G11" s="2">
         <v>44686</v>
@@ -1693,24 +1699,24 @@
         <v>72.75</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>129</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G12" s="2">
         <v>44686</v>
@@ -1773,24 +1779,24 @@
         <v>21.68</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>130</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G13" t="s">
         <v>120</v>
@@ -1853,24 +1859,24 @@
         <v>33.78</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>131</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G14" t="s">
         <v>121</v>
@@ -1933,24 +1939,24 @@
         <v>46.85</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>132</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G15" t="s">
         <v>122</v>
@@ -2013,24 +2019,24 @@
         <v>63.73</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>133</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G16" s="2">
         <v>44441</v>
@@ -2098,19 +2104,19 @@
         <v>134</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G17" s="2">
         <v>44077</v>
@@ -2178,19 +2184,19 @@
         <v>135</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G18" t="s">
         <v>123</v>
@@ -2258,19 +2264,19 @@
         <v>136</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G19" t="s">
         <v>124</v>
@@ -2338,19 +2344,19 @@
         <v>137</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G20" t="s">
         <v>123</v>
@@ -2418,19 +2424,19 @@
         <v>138</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G21" s="2">
         <v>44441</v>
@@ -2498,19 +2504,19 @@
         <v>139</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G22" t="s">
         <v>125</v>
@@ -2578,19 +2584,19 @@
         <v>140</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G23" s="2">
         <v>44441</v>
@@ -2658,19 +2664,19 @@
         <v>141</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G24" s="2">
         <v>44471</v>
@@ -2738,19 +2744,19 @@
         <v>142</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G25" s="2">
         <v>44206</v>
@@ -2818,19 +2824,19 @@
         <v>143</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G26" t="s">
         <v>126</v>
@@ -2898,19 +2904,19 @@
         <v>144</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2025</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G27" s="2">
         <v>43720</v>
@@ -2978,19 +2984,19 @@
         <v>145</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2025</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G28" s="2">
         <v>43720</v>
@@ -3058,19 +3064,19 @@
         <v>146</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>2025</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G29" t="s">
         <v>127</v>
@@ -3138,19 +3144,19 @@
         <v>147</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>2025</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G30" t="s">
         <v>128</v>
@@ -3218,19 +3224,19 @@
         <v>148</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>2025</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G31" t="s">
         <v>128</v>
@@ -3298,19 +3304,19 @@
         <v>149</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>2025</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G32" t="s">
         <v>128</v>
@@ -3378,22 +3384,22 @@
         <v>150</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33">
         <v>2025</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" t="s">
-        <v>101</v>
-      </c>
-      <c r="G33" t="s">
-        <v>129</v>
+        <v>102</v>
+      </c>
+      <c r="G33" s="2">
+        <v>43720</v>
       </c>
       <c r="H33">
         <v>51777</v>
@@ -3458,22 +3464,22 @@
         <v>151</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34">
         <v>2025</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H34">
         <v>50842</v>
@@ -3538,22 +3544,22 @@
         <v>152</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35">
         <v>2025</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G35" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H35">
         <v>96387</v>
@@ -3618,22 +3624,22 @@
         <v>153</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D36">
         <v>2025</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H36">
         <v>19372</v>
@@ -3698,19 +3704,19 @@
         <v>154</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D37">
         <v>2025</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G37" s="2">
         <v>44686</v>
@@ -3778,19 +3784,19 @@
         <v>155</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D38">
         <v>2025</v>
       </c>
       <c r="E38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F38" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G38" s="2">
         <v>44902</v>
@@ -3858,22 +3864,22 @@
         <v>156</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D39">
         <v>2025</v>
       </c>
       <c r="E39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F39" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G39" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H39">
         <v>108025</v>
@@ -3938,19 +3944,19 @@
         <v>157</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D40">
         <v>2025</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F40" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G40" t="s">
         <v>123</v>
@@ -4018,22 +4024,22 @@
         <v>158</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D41">
         <v>2025</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F41" t="s">
-        <v>102</v>
-      </c>
-      <c r="G41" t="s">
-        <v>129</v>
+        <v>103</v>
+      </c>
+      <c r="G41" s="2">
+        <v>43475</v>
       </c>
       <c r="H41">
         <v>101219</v>
@@ -4098,22 +4104,22 @@
         <v>159</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D42">
         <v>2025</v>
       </c>
       <c r="E42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F42" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G42" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H42">
         <v>175342</v>
@@ -4178,19 +4184,19 @@
         <v>160</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D43">
         <v>2025</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F43" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G43" s="2">
         <v>45514</v>
@@ -4258,19 +4264,19 @@
         <v>161</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D44">
         <v>2025</v>
       </c>
       <c r="E44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F44" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G44" t="s">
         <v>133</v>
@@ -4338,22 +4344,22 @@
         <v>162</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D45">
         <v>2025</v>
       </c>
       <c r="E45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F45" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G45" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H45">
         <v>52098</v>
@@ -4418,19 +4424,19 @@
         <v>163</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D46">
         <v>2025</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F46" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G46" s="2">
         <v>45451</v>
@@ -4498,19 +4504,19 @@
         <v>164</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D47">
         <v>2025</v>
       </c>
       <c r="E47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F47" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G47" s="2">
         <v>45451</v>
@@ -4578,19 +4584,19 @@
         <v>165</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D48">
         <v>2025</v>
       </c>
       <c r="E48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F48" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G48" t="s">
         <v>122</v>
@@ -4658,19 +4664,19 @@
         <v>166</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D49">
         <v>2025</v>
       </c>
       <c r="E49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G49" t="s">
         <v>122</v>
@@ -4738,19 +4744,19 @@
         <v>167</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D50">
         <v>2025</v>
       </c>
       <c r="E50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G50" s="2">
         <v>45080</v>
@@ -4818,19 +4824,19 @@
         <v>168</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D51">
         <v>2025</v>
       </c>
       <c r="E51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F51" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G51" s="2">
         <v>45080</v>
@@ -4898,19 +4904,19 @@
         <v>169</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D52">
         <v>2025</v>
       </c>
       <c r="E52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F52" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G52" s="2">
         <v>44631</v>
@@ -4978,19 +4984,19 @@
         <v>170</v>
       </c>
       <c r="B53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D53">
         <v>2025</v>
       </c>
       <c r="E53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F53" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G53" s="2">
         <v>45839</v>
@@ -5058,22 +5064,22 @@
         <v>171</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D54">
         <v>2025</v>
       </c>
       <c r="E54" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F54" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G54" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H54">
         <v>4540</v>
@@ -5138,22 +5144,22 @@
         <v>172</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D55">
         <v>2025</v>
       </c>
       <c r="E55" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F55" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G55" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H55">
         <v>69676</v>
@@ -5218,22 +5224,22 @@
         <v>173</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D56">
         <v>2025</v>
       </c>
       <c r="E56" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F56" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G56" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H56">
         <v>37555</v>
@@ -5298,19 +5304,19 @@
         <v>174</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D57">
         <v>2025</v>
       </c>
       <c r="E57" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F57" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G57" s="2">
         <v>44748</v>
@@ -5378,19 +5384,19 @@
         <v>175</v>
       </c>
       <c r="B58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D58">
         <v>2025</v>
       </c>
       <c r="E58" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F58" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G58" s="2">
         <v>44686</v>
@@ -5458,22 +5464,22 @@
         <v>176</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D59">
         <v>2025</v>
       </c>
       <c r="E59" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F59" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G59" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H59">
         <v>19685</v>
@@ -5538,22 +5544,22 @@
         <v>177</v>
       </c>
       <c r="B60" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D60">
         <v>2025</v>
       </c>
       <c r="E60" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F60" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G60" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H60">
         <v>27279</v>
@@ -5618,22 +5624,22 @@
         <v>178</v>
       </c>
       <c r="B61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D61">
         <v>2025</v>
       </c>
       <c r="E61" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F61" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H61">
         <v>46840</v>
@@ -5698,19 +5704,19 @@
         <v>179</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D62">
         <v>2025</v>
       </c>
       <c r="E62" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F62" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G62" s="2">
         <v>44960</v>
@@ -5778,22 +5784,22 @@
         <v>180</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D63">
         <v>2025</v>
       </c>
       <c r="E63" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F63" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H63">
         <v>49428</v>
@@ -5858,22 +5864,22 @@
         <v>181</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D64">
         <v>2025</v>
       </c>
       <c r="E64" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F64" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H64">
         <v>190</v>
@@ -5938,22 +5944,22 @@
         <v>182</v>
       </c>
       <c r="B65" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C65" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D65">
         <v>2025</v>
       </c>
       <c r="E65" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F65" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H65">
         <v>90</v>
@@ -6018,19 +6024,19 @@
         <v>183</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C66" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D66">
         <v>2025</v>
       </c>
       <c r="E66" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F66" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G66" s="2">
         <v>45907</v>
@@ -6098,22 +6104,22 @@
         <v>184</v>
       </c>
       <c r="B67" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C67" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D67">
         <v>2025</v>
       </c>
       <c r="E67" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F67" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G67" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H67">
         <v>1402</v>
@@ -6178,22 +6184,22 @@
         <v>185</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D68">
         <v>2025</v>
       </c>
       <c r="E68" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F68" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G68" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H68">
         <v>50099</v>
@@ -6258,22 +6264,22 @@
         <v>186</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D69">
         <v>2025</v>
       </c>
       <c r="E69" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F69" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G69" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H69">
         <v>22109</v>
@@ -6338,22 +6344,22 @@
         <v>187</v>
       </c>
       <c r="B70" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C70" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D70">
         <v>2025</v>
       </c>
       <c r="E70" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F70" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G70" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H70">
         <v>40668</v>
@@ -6418,22 +6424,22 @@
         <v>188</v>
       </c>
       <c r="B71" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C71" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D71">
         <v>2025</v>
       </c>
       <c r="E71" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F71" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G71" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H71">
         <v>24784</v>
@@ -6498,22 +6504,22 @@
         <v>189</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D72">
         <v>2025</v>
       </c>
       <c r="E72" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F72" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G72" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H72">
         <v>8344</v>
@@ -6578,22 +6584,22 @@
         <v>190</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D73">
         <v>2025</v>
       </c>
       <c r="E73" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G73" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H73">
         <v>7741</v>
@@ -6658,22 +6664,22 @@
         <v>191</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C74" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D74">
         <v>2025</v>
       </c>
       <c r="E74" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F74" t="s">
         <v>116</v>
       </c>
       <c r="G74" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H74">
         <v>17278</v>
